--- a/城市-商品.xlsx
+++ b/城市-商品.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProject\cursor-ai-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ni339\Downloads\整合本体包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E831AA8-EAD9-44A3-BB6F-81341C6DA02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25236FEF-7BEA-4B8E-B052-987296613E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="0" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="189">
   <si>
     <t>修格里城</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,256 +87,689 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>坚果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海盐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁盟哨站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防弹背心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑胶炸药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汽油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靛红五月军用食品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>澄明数据中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扬声器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏卡带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>录像带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荧光棒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火车玩具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔能源研究所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔小型桦树发电机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石墨烯电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔101民用无人机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用太阳能电池组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锂电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>充电电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔战备工厂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火澄石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负片炮弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔202军用无人机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗污染防护服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钛合金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碳纤维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形态共振瞄准器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高导磁硅钢片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄铜线圈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒原站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琥珀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔雀石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿松石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棉花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铅矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石墨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曼德矿场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图形加速卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钛矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁轨用特种钢材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曼德工具箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢筋混凝土轨枕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄铜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砂石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淘金乐园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青金石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛瑙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漆黑矿渣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石英砂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7号自由港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿妮塔发射中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航天半导体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太阳电池阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜂窝防热烧蚀材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高导热陶瓷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>镍基高温合金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>液氧甲烷燃料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无刷电机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火箭拼装玩具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>录音带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海角城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>珍珠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大龙虾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行李箱包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>户外用品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海角辣椒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯棉布料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>斑节虾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坚果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>啤酒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>海盐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁盟哨站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防弹背心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炮弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精钢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>塑胶炸药</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汽油</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>靛红五月军用食品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>澄明数据中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>银矿石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扬声器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏卡带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>录像带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荧光棒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火车玩具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿妮塔能源研究所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿妮塔小型桦树发电机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石墨烯电池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿妮塔101民用无人机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家用太阳能电池组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锂电池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>充电电池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿妮塔战备工厂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火澄石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负片炮弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿妮塔202军用无人机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抗污染防护服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钛合金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碳纤维</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>形态共振瞄准器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高导磁硅钢片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄铜线圈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒原站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琥珀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孔雀石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绿松石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>棉花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铅矿石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石墨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>土豆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>曼德矿场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图形加速卡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钛矿石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁轨用特种钢材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>曼德工具箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢筋混凝土轨枕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁矿石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄铜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>砂石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淘金乐园</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>青金石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛瑙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漆黑矿渣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石英砂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7号自由港</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯棉T恤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花呢上衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无纺布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛仔裤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蕾丝连衣裙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单晶硅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学会书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云岫桥基地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚麻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫工具包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尼龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绣线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛仔布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>涤纶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肥皂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇流塔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼肝油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学会纪念品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝王蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芳纶纤维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水银</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香薰蜡烛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马鲛鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贻贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法兰绒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远星大桥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复合钢索</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>象拔蚌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨铁矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄武岩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扇贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水泥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岚心城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>栖羽站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金箔酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随身听</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>画材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纳豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羽绒睡袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹅绒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树脂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羽绒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑毛牛排</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岚心锦服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹅绒被</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔图站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石蜡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硅矿石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄铁矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石灰岩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定公仔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游乐城主题配饰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定典藏游戏卡带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游乐城纪念唱片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纪念卫衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城堡摆件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛绒玩具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游乐城纪念徽章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游乐城纪念文具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑月游乐城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贡露城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼子酱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火腿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻奢女装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶工艺品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白兰地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>化妆品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>橄榄油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日化用品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武林源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明前龙井</t>
+  </si>
+  <si>
+    <t>龙井茶</t>
+  </si>
+  <si>
+    <t>武林丝绸</t>
+  </si>
+  <si>
+    <t>羽纸扇</t>
+  </si>
+  <si>
+    <t>临安山核桃</t>
+  </si>
+  <si>
+    <t>西湖醋鱼</t>
+  </si>
+  <si>
+    <t>西湖藕粉</t>
+  </si>
+  <si>
+    <t>叫化童鸡</t>
+  </si>
+  <si>
+    <t>杭白菊</t>
+  </si>
+  <si>
+    <t>笋干</t>
   </si>
 </sst>
 </file>
@@ -661,10 +1094,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,27 +1111,30 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -716,213 +1152,565 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>46</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>49</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="J6" t="s">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>58</v>
       </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>60</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>61</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>62</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>63</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>65</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>69</v>
       </c>
-      <c r="K8" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>71</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
         <v>75</v>
       </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" t="s">
-        <v>76</v>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>141</v>
+      </c>
+      <c r="J15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" t="s">
+        <v>148</v>
+      </c>
+      <c r="I16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" t="s">
+        <v>186</v>
+      </c>
+      <c r="J20" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
